--- a/SGC-CKN/Excel/be61efe0-413f-4a8c-a9cf-26a302adeea2_Lô_CT-02_P8-12_D800_09-04-2026.xlsx
+++ b/SGC-CKN/Excel/be61efe0-413f-4a8c-a9cf-26a302adeea2_Lô_CT-02_P8-12_D800_09-04-2026.xlsx
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">10:00
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:29
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t/>
@@ -116,11 +116,11 @@
   </si>
   <si>
     <t xml:space="preserve">10:25
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:32
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -129,12 +129,12 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">10:35
-08/04/2026</t>
+    <t xml:space="preserve">10:33
+09/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">11:59
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -144,11 +144,11 @@
   </si>
   <si>
     <t xml:space="preserve">13:00
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">13:49
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -158,11 +158,11 @@
   </si>
   <si>
     <t xml:space="preserve">13:50
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">14:35
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -172,11 +172,11 @@
   </si>
   <si>
     <t xml:space="preserve">14:36
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">16:05
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -186,11 +186,11 @@
   </si>
   <si>
     <t xml:space="preserve">16:06
-08/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:45
-08/04/2026</t>
+09/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:43
+09/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -199,12 +199,12 @@
     <t>TK-16.1.Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">16:46
-08/04/2026</t>
+    <t xml:space="preserve">16:44
+09/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:05
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -214,11 +214,11 @@
   </si>
   <si>
     <t xml:space="preserve">17:10
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">18:07
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -228,11 +228,11 @@
   </si>
   <si>
     <t xml:space="preserve">18:08
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">18:25
-08/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1315,13 +1315,13 @@
         <v>-17.5</v>
       </c>
       <c r="H13" s="12">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="I13" s="12">
         <v>8.2</v>
       </c>
       <c r="J13" s="8">
-        <v>5.86</v>
+        <v>5.72</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1455,13 +1455,13 @@
         <v>-38.3</v>
       </c>
       <c r="H17" s="24">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="I17" s="24">
         <v>2.5</v>
       </c>
       <c r="J17" s="27">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>30</v>
@@ -1490,13 +1490,13 @@
         <v>-39.3</v>
       </c>
       <c r="H18" s="28">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="I18" s="28">
         <v>1</v>
       </c>
       <c r="J18" s="27">
-        <v>3.16</v>
+        <v>2.86</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1785,13 +1785,13 @@
         <v>-17.5</v>
       </c>
       <c r="G4" s="12">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H4" s="12">
         <v>8.2</v>
       </c>
       <c r="I4" s="8">
-        <v>5.86</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1901,13 +1901,13 @@
         <v>-38.3</v>
       </c>
       <c r="G8" s="24">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H8" s="24">
         <v>2.5</v>
       </c>
       <c r="I8" s="27">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1930,13 +1930,13 @@
         <v>-39.3</v>
       </c>
       <c r="G9" s="28">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="H9" s="28">
         <v>1</v>
       </c>
       <c r="I9" s="27">
-        <v>3.16</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2017,13 +2017,13 @@
         <v>-44.58</v>
       </c>
       <c r="G12" s="39">
-        <v>7.25</v>
+        <v>7.28</v>
       </c>
       <c r="H12" s="39">
         <v>43.68</v>
       </c>
       <c r="I12" s="39">
-        <v>6.02</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/be61efe0-413f-4a8c-a9cf-26a302adeea2_Lô_CT-02_P8-12_D800_09-04-2026.xlsx
+++ b/SGC-CKN/Excel/be61efe0-413f-4a8c-a9cf-26a302adeea2_Lô_CT-02_P8-12_D800_09-04-2026.xlsx
@@ -1239,19 +1239,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-7.5</v>
+        <v>-7.3</v>
       </c>
       <c r="H11" s="5">
         <v>0.48</v>
       </c>
       <c r="I11" s="5">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="J11" s="8">
-        <v>13.66</v>
+        <v>15.1</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1274,7 +1274,7 @@
         <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>-7.5</v>
+        <v>-7.3</v>
       </c>
       <c r="G12" s="9">
         <v>-9.3</v>
@@ -1283,10 +1283,10 @@
         <v>0.12</v>
       </c>
       <c r="I12" s="9">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J12" s="8">
-        <v>15.43</v>
+        <v>17.14</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1721,19 +1721,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-7.5</v>
+        <v>-7.3</v>
       </c>
       <c r="G2" s="5">
         <v>0.48</v>
       </c>
       <c r="H2" s="5">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="I2" s="8">
-        <v>13.66</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1750,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-7.5</v>
+        <v>-7.3</v>
       </c>
       <c r="F3" s="9">
         <v>-9.3</v>
@@ -1759,10 +1759,10 @@
         <v>0.12</v>
       </c>
       <c r="H3" s="9">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I3" s="8">
-        <v>15.43</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2011,7 +2011,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-44.58</v>
@@ -2020,10 +2020,10 @@
         <v>7.28</v>
       </c>
       <c r="H12" s="39">
-        <v>43.68</v>
+        <v>44.58</v>
       </c>
       <c r="I12" s="39">
-        <v>6</v>
+        <v>6.12</v>
       </c>
     </row>
   </sheetData>
